--- a/Multi-Template Computational Graph/Excels/SixNode_Verification.xlsx
+++ b/Multi-Template Computational Graph/Excels/SixNode_Verification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xwu03\Nutstore\1\Coding\Template\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2C2694-831B-4639-9B5D-DB1FDDB7A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8256E26A-DA32-4109-B18F-C21783C8F6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,16 +190,16 @@
     <t>The model is fitted on the links with a sensor only; the errors are taken on all nine links.</t>
   </si>
   <si>
-    <t>One template (S = 1): the model can only scale the template, β v_s, so observations made from several templates are not reproduced.</t>
+    <t>One template (S = 1): the model can only scale the template, η v_s, so observations made from several templates are not reproduced.</t>
   </si>
   <si>
     <t>Four templates (S = 4): the model fits the weights λ^m and reproduces every observation, including l5 and l6.</t>
   </si>
   <si>
-    <t>Table 1  One template: best scale β for each observation (rows) and template (columns)</t>
-  </si>
-  <si>
-    <t>Formula: β = Σ_sensor v̄^m · v_s / Σ_sensor v_s · v_s   (least squares on the links with a sensor)</t>
+    <t>Table 1  One template: best scale η for each observation (rows) and template (columns)</t>
+  </si>
+  <si>
+    <t>Formula: η = Σ_sensor v̄^m · v_s / Σ_sensor v_s · v_s   (least squares on the links with a sensor)</t>
   </si>
   <si>
     <t>Table 2  Four templates: estimated weights λ^m (compare with the assumed weights in sheet 2)</t>
@@ -211,7 +211,7 @@
     <t>Table 3  Errors over the five observations and all nine links</t>
   </si>
   <si>
-    <t>Formula: estimate = β v_s (one template) or Σ_s λ_s^m v_s (four templates); RMSE and MAE over 45 values; MAPE = mean over observations of mean |error| / v̄ (v̄ &gt; 0)</t>
+    <t>Formula: estimate = η v_s (one template) or Σ_s λ_s^m v_s (four templates); RMSE and MAE over 45 values; MAPE = mean over observations of mean |error| / v̄ (v̄ &gt; 0)</t>
   </si>
   <si>
     <t>Model</t>
@@ -244,7 +244,7 @@
     <t>Table 4  Example: observation 5 (made from all four templates)</t>
   </si>
   <si>
-    <t>Formula: one template: β v_s;  four templates: Σ_s λ_s^5 v_s</t>
+    <t>Formula: one template: η v_s;  four templates: Σ_s λ_s^5 v_s</t>
   </si>
   <si>
     <t>Link flows</t>
